--- a/static/sapo_mau_file_nhap_don_nhap_hang-1-min.xlsx
+++ b/static/sapo_mau_file_nhap_don_nhap_hang-1-min.xlsx
@@ -415,155 +415,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>tc={006A0038-003E-4F8E-828B-00AF00F700BD}</author>
-    <author>tc={008800B7-0010-41A3-9E7E-00BC00370029}</author>
-    <author>tc={00FB008A-005B-43E4-B345-002300A50092}</author>
-    <author>tc={009C00D1-0037-4472-B7DC-00A5001300E1}</author>
-    <author>tc={00940099-00A2-459D-AF23-00EB008D006E}</author>
-    <author>tc={00A30015-00E1-4311-B922-00EA00750062}</author>
-    <author>tc={000B00D0-00BD-4981-B1BC-003800300021}</author>
-    <author>tc={00750066-004E-4C93-9538-00C400380086}</author>
-    <author>tc={00B00070-008B-4642-917A-00BA000B0061}</author>
-    <author>tc={005F0049-005B-47FD-ACFA-00C1005B0018}</author>
-    <author>tc={009B0085-0051-4514-800C-003C003300D0}</author>
-    <author>tc={00F90092-006B-4297-9BD4-00050049008A}</author>
-    <author>tc={00EF006A-003D-4CD7-8683-00CD004C0077}</author>
-    <author>tc={005700F4-00ED-4986-B0C4-00A4002B0098}</author>
-    <author>tc={00B80097-00BB-4B41-8F1C-002900D60006}</author>
-    <author>tc={003900CF-00DC-48A1-80FF-007200640008}</author>
-    <author>tc={008200E5-00C2-4661-BDB5-00CE00730007}</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Trường không bắt buộc. Nếu để trống, đơn nhập sẽ lấy mã hệ thống tự sinh. Vui lòng điền mã đơn nhập vào ô kế bên phải
-</t>
-      </text>
-    </comment>
-    <comment ref="A2" authorId="1" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Trường không bắt buộc. Cần nhập chính xác mã chính sách giá trên Sapo. Nếu để trống khi tạo đơn nhập sẽ lấy giá người dùng cung cấp trên cột "giá nhập", khi nhập mã sẽ lấy theo giá có sẵn trên Sapo ứng với mã người dùng nhập. Vui lòng điền mã chính sách giá vào ô kế bên phải.
-</t>
-      </text>
-    </comment>
-    <comment ref="T5" authorId="2" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Mỗi dòng trên cột chi phí tổng đơn sẽ tạo ra một chi phí trên đơn nhập hàng. Có thể tạo ra nhiều dòng chi phí
-</t>
-      </text>
-    </comment>
-    <comment ref="V5" authorId="3" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Chỉ cần nhập một trong hai loại giá trị theo % hoặc theo VND
-Trường hợp nhập cả hai cột trên cùng một hàng, Sapo sẽ lấy giá trị tiền
-</t>
-      </text>
-    </comment>
-    <comment ref="A6" authorId="4" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Trường SKU sản phẩm bắt buộc nhập chính xác. Nếu để trống cần phải nhập mã Barcode sản phẩm
-</t>
-      </text>
-    </comment>
-    <comment ref="B6" authorId="5" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Nếu mã SKU trống, cần phải nhập mã Barcode. Nếu cửa hàng có nhiều sản phẩm trùng mã Barcode Sapo sẽ lấy sản phẩm tạo gần nhất.
-</t>
-      </text>
-    </comment>
-    <comment ref="D6" authorId="6" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Trường bắt buộc nhập. Chỉ được nhập số trong khoảng 0 &lt;n&lt; 999,999
-</t>
-      </text>
-    </comment>
-    <comment ref="N6" authorId="7" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Nhập serial/ imei của từng sản phẩm. Ngăn cách các serial bằng dấu phẩy (,)
-</t>
-      </text>
-    </comment>
-    <comment ref="O6" authorId="8" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Chỉ được nhập số nguyên trong khoảng 0-99,999,999. Trường hợp để trống sẽ lấy đơn giá là đơn giá mặc định của sản phẩm lưu trên hệ thống
-</t>
-      </text>
-    </comment>
-    <comment ref="P6" authorId="9" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Chỉ cần nhập một trong hai loại giá trị theo % hoặc theo VND
-Trường hợp nhập cả hai cột trên cùng một hàng, Sapo sẽ lấy giá trị tiền
-</t>
-      </text>
-    </comment>
-    <comment ref="R6" authorId="10" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Chỉ được nhập số trong khoảng o &lt; n &lt;=100
-Nếu Áp dụng thuế theo cấu hình sản phẩm, không cần nhập giá trị thuế
-</t>
-      </text>
-    </comment>
-    <comment ref="S6" authorId="11" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Ghi chú cho từng sản phẩm. Tối đa 500 ký tự
-</t>
-      </text>
-    </comment>
-    <comment ref="U6" authorId="12" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Nhập số nguyên trong khoảng 0-99,999,999
-</t>
-      </text>
-    </comment>
-    <comment ref="W6" authorId="13" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Nhập số nguyên, giá trị tối đa bằng tổng giá trị hàng hoá nhập
-</t>
-      </text>
-    </comment>
-    <comment ref="L7" authorId="14" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Nhập ngày sản xuất định dạng dd/mm/yyyy
-</t>
-      </text>
-    </comment>
-    <comment ref="M7" authorId="15" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Nhập ngày hết hạn theo định dạng dd/mm/yyyy
-Đây là trường thông tin bắt buộc nếu nhập lô sản phẩm.
-</t>
-      </text>
-    </comment>
-    <comment ref="Q7" authorId="16" shapeId="0">
-      <text>
-        <t xml:space="preserve">SAPO:
-Nhập số nguyên tối đa bằng giá trị (đơn giá x số lượng)
-</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -819,6 +670,7 @@
     <row r="3">
       <c r="K3" s="4" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
@@ -13553,6 +13405,5 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>